--- a/artfynd/A 59271-2025 artfynd.xlsx
+++ b/artfynd/A 59271-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,9 +799,918 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136954257</v>
+      </c>
+      <c r="B3" t="n">
+        <v>108116</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Söder Rälta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>500514</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6721467</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136954257</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136954258</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98282</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Söder Rälta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>500508</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6721461</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136954258</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136954251</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100017</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Söder Rälta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>500579</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6721584</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136954251</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136954253</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100017</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Söder Rälta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>500565</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6721560</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136954253</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136954254</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100017</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Söder Rälta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>500559</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6721548</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136954254</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136954255</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100017</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Söder Rälta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>500546</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6721524</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136954255</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136954256</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100017</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Söder Rälta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>500533</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6721503</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136954256</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136954252</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99390</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Söder Rälta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>500573</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6721571</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136954252</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59271-2025 artfynd.xlsx
+++ b/artfynd/A 59271-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136954257</v>
       </c>
       <c r="B3" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136954258</v>
       </c>
       <c r="B4" t="n">
-        <v>98282</v>
+        <v>98288</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136954251</v>
       </c>
       <c r="B5" t="n">
-        <v>100017</v>
+        <v>100023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136954253</v>
       </c>
       <c r="B6" t="n">
-        <v>100017</v>
+        <v>100023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136954254</v>
       </c>
       <c r="B7" t="n">
-        <v>100017</v>
+        <v>100023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136954255</v>
       </c>
       <c r="B8" t="n">
-        <v>100017</v>
+        <v>100023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136954256</v>
       </c>
       <c r="B9" t="n">
-        <v>100017</v>
+        <v>100023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>136954252</v>
       </c>
       <c r="B10" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59271-2025 artfynd.xlsx
+++ b/artfynd/A 59271-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136954257</v>
       </c>
       <c r="B3" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136954258</v>
       </c>
       <c r="B4" t="n">
-        <v>98288</v>
+        <v>98290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136954251</v>
       </c>
       <c r="B5" t="n">
-        <v>100023</v>
+        <v>100025</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136954253</v>
       </c>
       <c r="B6" t="n">
-        <v>100023</v>
+        <v>100025</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136954254</v>
       </c>
       <c r="B7" t="n">
-        <v>100023</v>
+        <v>100025</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136954255</v>
       </c>
       <c r="B8" t="n">
-        <v>100023</v>
+        <v>100025</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136954256</v>
       </c>
       <c r="B9" t="n">
-        <v>100023</v>
+        <v>100025</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>136954252</v>
       </c>
       <c r="B10" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59271-2025 artfynd.xlsx
+++ b/artfynd/A 59271-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136954257</v>
       </c>
       <c r="B3" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136954258</v>
       </c>
       <c r="B4" t="n">
-        <v>98290</v>
+        <v>98291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136954251</v>
       </c>
       <c r="B5" t="n">
-        <v>100025</v>
+        <v>100026</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136954253</v>
       </c>
       <c r="B6" t="n">
-        <v>100025</v>
+        <v>100026</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136954254</v>
       </c>
       <c r="B7" t="n">
-        <v>100025</v>
+        <v>100026</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136954255</v>
       </c>
       <c r="B8" t="n">
-        <v>100025</v>
+        <v>100026</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136954256</v>
       </c>
       <c r="B9" t="n">
-        <v>100025</v>
+        <v>100026</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>136954252</v>
       </c>
       <c r="B10" t="n">
-        <v>99398</v>
+        <v>99399</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59271-2025 artfynd.xlsx
+++ b/artfynd/A 59271-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136954257</v>
       </c>
       <c r="B3" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136954258</v>
       </c>
       <c r="B4" t="n">
-        <v>98291</v>
+        <v>98297</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136954251</v>
       </c>
       <c r="B5" t="n">
-        <v>100026</v>
+        <v>100032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136954253</v>
       </c>
       <c r="B6" t="n">
-        <v>100026</v>
+        <v>100032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136954254</v>
       </c>
       <c r="B7" t="n">
-        <v>100026</v>
+        <v>100032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136954255</v>
       </c>
       <c r="B8" t="n">
-        <v>100026</v>
+        <v>100032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136954256</v>
       </c>
       <c r="B9" t="n">
-        <v>100026</v>
+        <v>100032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>136954252</v>
       </c>
       <c r="B10" t="n">
-        <v>99399</v>
+        <v>99405</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59271-2025 artfynd.xlsx
+++ b/artfynd/A 59271-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136954257</v>
       </c>
       <c r="B3" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136954258</v>
       </c>
       <c r="B4" t="n">
-        <v>98297</v>
+        <v>98301</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136954251</v>
       </c>
       <c r="B5" t="n">
-        <v>100032</v>
+        <v>100036</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136954253</v>
       </c>
       <c r="B6" t="n">
-        <v>100032</v>
+        <v>100036</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136954254</v>
       </c>
       <c r="B7" t="n">
-        <v>100032</v>
+        <v>100036</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136954255</v>
       </c>
       <c r="B8" t="n">
-        <v>100032</v>
+        <v>100036</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136954256</v>
       </c>
       <c r="B9" t="n">
-        <v>100032</v>
+        <v>100036</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>136954252</v>
       </c>
       <c r="B10" t="n">
-        <v>99405</v>
+        <v>99409</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59271-2025 artfynd.xlsx
+++ b/artfynd/A 59271-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136954257</v>
       </c>
       <c r="B3" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136954258</v>
       </c>
       <c r="B4" t="n">
-        <v>98301</v>
+        <v>98303</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136954251</v>
       </c>
       <c r="B5" t="n">
-        <v>100036</v>
+        <v>100038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136954253</v>
       </c>
       <c r="B6" t="n">
-        <v>100036</v>
+        <v>100038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136954254</v>
       </c>
       <c r="B7" t="n">
-        <v>100036</v>
+        <v>100038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136954255</v>
       </c>
       <c r="B8" t="n">
-        <v>100036</v>
+        <v>100038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136954256</v>
       </c>
       <c r="B9" t="n">
-        <v>100036</v>
+        <v>100038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>136954252</v>
       </c>
       <c r="B10" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59271-2025 artfynd.xlsx
+++ b/artfynd/A 59271-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136954257</v>
       </c>
       <c r="B3" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136954258</v>
       </c>
       <c r="B4" t="n">
-        <v>98303</v>
+        <v>98305</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136954251</v>
       </c>
       <c r="B5" t="n">
-        <v>100038</v>
+        <v>100040</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136954253</v>
       </c>
       <c r="B6" t="n">
-        <v>100038</v>
+        <v>100040</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136954254</v>
       </c>
       <c r="B7" t="n">
-        <v>100038</v>
+        <v>100040</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136954255</v>
       </c>
       <c r="B8" t="n">
-        <v>100038</v>
+        <v>100040</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136954256</v>
       </c>
       <c r="B9" t="n">
-        <v>100038</v>
+        <v>100040</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>136954252</v>
       </c>
       <c r="B10" t="n">
-        <v>99411</v>
+        <v>99413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59271-2025 artfynd.xlsx
+++ b/artfynd/A 59271-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136954257</v>
       </c>
       <c r="B3" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136954258</v>
       </c>
       <c r="B4" t="n">
-        <v>98305</v>
+        <v>98318</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136954251</v>
       </c>
       <c r="B5" t="n">
-        <v>100040</v>
+        <v>100053</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136954253</v>
       </c>
       <c r="B6" t="n">
-        <v>100040</v>
+        <v>100053</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136954254</v>
       </c>
       <c r="B7" t="n">
-        <v>100040</v>
+        <v>100053</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136954255</v>
       </c>
       <c r="B8" t="n">
-        <v>100040</v>
+        <v>100053</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136954256</v>
       </c>
       <c r="B9" t="n">
-        <v>100040</v>
+        <v>100053</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>136954252</v>
       </c>
       <c r="B10" t="n">
-        <v>99413</v>
+        <v>99426</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59271-2025 artfynd.xlsx
+++ b/artfynd/A 59271-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136954257</v>
       </c>
       <c r="B3" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136954258</v>
       </c>
       <c r="B4" t="n">
-        <v>98318</v>
+        <v>98320</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136954251</v>
       </c>
       <c r="B5" t="n">
-        <v>100053</v>
+        <v>100055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136954253</v>
       </c>
       <c r="B6" t="n">
-        <v>100053</v>
+        <v>100055</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136954254</v>
       </c>
       <c r="B7" t="n">
-        <v>100053</v>
+        <v>100055</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136954255</v>
       </c>
       <c r="B8" t="n">
-        <v>100053</v>
+        <v>100055</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136954256</v>
       </c>
       <c r="B9" t="n">
-        <v>100053</v>
+        <v>100055</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>136954252</v>
       </c>
       <c r="B10" t="n">
-        <v>99426</v>
+        <v>99428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59271-2025 artfynd.xlsx
+++ b/artfynd/A 59271-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136954257</v>
       </c>
       <c r="B3" t="n">
-        <v>108154</v>
+        <v>108158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136954258</v>
       </c>
       <c r="B4" t="n">
-        <v>98320</v>
+        <v>98323</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136954251</v>
       </c>
       <c r="B5" t="n">
-        <v>100055</v>
+        <v>100058</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136954253</v>
       </c>
       <c r="B6" t="n">
-        <v>100055</v>
+        <v>100058</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136954254</v>
       </c>
       <c r="B7" t="n">
-        <v>100055</v>
+        <v>100058</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136954255</v>
       </c>
       <c r="B8" t="n">
-        <v>100055</v>
+        <v>100058</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136954256</v>
       </c>
       <c r="B9" t="n">
-        <v>100055</v>
+        <v>100058</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>136954252</v>
       </c>
       <c r="B10" t="n">
-        <v>99428</v>
+        <v>99431</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59271-2025 artfynd.xlsx
+++ b/artfynd/A 59271-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136954257</v>
       </c>
       <c r="B3" t="n">
-        <v>108158</v>
+        <v>108179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136954258</v>
       </c>
       <c r="B4" t="n">
-        <v>98323</v>
+        <v>98333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136954251</v>
       </c>
       <c r="B5" t="n">
-        <v>100058</v>
+        <v>100068</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136954253</v>
       </c>
       <c r="B6" t="n">
-        <v>100058</v>
+        <v>100068</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136954254</v>
       </c>
       <c r="B7" t="n">
-        <v>100058</v>
+        <v>100068</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136954255</v>
       </c>
       <c r="B8" t="n">
-        <v>100058</v>
+        <v>100068</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136954256</v>
       </c>
       <c r="B9" t="n">
-        <v>100058</v>
+        <v>100068</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>136954252</v>
       </c>
       <c r="B10" t="n">
-        <v>99431</v>
+        <v>99441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59271-2025 artfynd.xlsx
+++ b/artfynd/A 59271-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136954257</v>
       </c>
       <c r="B3" t="n">
-        <v>108179</v>
+        <v>108180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136954258</v>
       </c>
       <c r="B4" t="n">
-        <v>98333</v>
+        <v>98334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136954251</v>
       </c>
       <c r="B5" t="n">
-        <v>100068</v>
+        <v>100069</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136954253</v>
       </c>
       <c r="B6" t="n">
-        <v>100068</v>
+        <v>100069</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136954254</v>
       </c>
       <c r="B7" t="n">
-        <v>100068</v>
+        <v>100069</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136954255</v>
       </c>
       <c r="B8" t="n">
-        <v>100068</v>
+        <v>100069</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136954256</v>
       </c>
       <c r="B9" t="n">
-        <v>100068</v>
+        <v>100069</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>136954252</v>
       </c>
       <c r="B10" t="n">
-        <v>99441</v>
+        <v>99442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59271-2025 artfynd.xlsx
+++ b/artfynd/A 59271-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136954257</v>
       </c>
       <c r="B3" t="n">
-        <v>108180</v>
+        <v>108185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136954258</v>
       </c>
       <c r="B4" t="n">
-        <v>98334</v>
+        <v>98339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136954251</v>
       </c>
       <c r="B5" t="n">
-        <v>100069</v>
+        <v>100074</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136954253</v>
       </c>
       <c r="B6" t="n">
-        <v>100069</v>
+        <v>100074</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136954254</v>
       </c>
       <c r="B7" t="n">
-        <v>100069</v>
+        <v>100074</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136954255</v>
       </c>
       <c r="B8" t="n">
-        <v>100069</v>
+        <v>100074</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136954256</v>
       </c>
       <c r="B9" t="n">
-        <v>100069</v>
+        <v>100074</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>136954252</v>
       </c>
       <c r="B10" t="n">
-        <v>99442</v>
+        <v>99447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59271-2025 artfynd.xlsx
+++ b/artfynd/A 59271-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136954257</v>
       </c>
       <c r="B3" t="n">
-        <v>108185</v>
+        <v>108188</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136954258</v>
       </c>
       <c r="B4" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136954251</v>
       </c>
       <c r="B5" t="n">
-        <v>100074</v>
+        <v>100077</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136954253</v>
       </c>
       <c r="B6" t="n">
-        <v>100074</v>
+        <v>100077</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136954254</v>
       </c>
       <c r="B7" t="n">
-        <v>100074</v>
+        <v>100077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136954255</v>
       </c>
       <c r="B8" t="n">
-        <v>100074</v>
+        <v>100077</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136954256</v>
       </c>
       <c r="B9" t="n">
-        <v>100074</v>
+        <v>100077</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>136954252</v>
       </c>
       <c r="B10" t="n">
-        <v>99447</v>
+        <v>99449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59271-2025 artfynd.xlsx
+++ b/artfynd/A 59271-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136954257</v>
       </c>
       <c r="B3" t="n">
-        <v>108188</v>
+        <v>108194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136954258</v>
       </c>
       <c r="B4" t="n">
-        <v>98341</v>
+        <v>98347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136954251</v>
       </c>
       <c r="B5" t="n">
-        <v>100077</v>
+        <v>100083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136954253</v>
       </c>
       <c r="B6" t="n">
-        <v>100077</v>
+        <v>100083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136954254</v>
       </c>
       <c r="B7" t="n">
-        <v>100077</v>
+        <v>100083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136954255</v>
       </c>
       <c r="B8" t="n">
-        <v>100077</v>
+        <v>100083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136954256</v>
       </c>
       <c r="B9" t="n">
-        <v>100077</v>
+        <v>100083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>136954252</v>
       </c>
       <c r="B10" t="n">
-        <v>99449</v>
+        <v>99455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59271-2025 artfynd.xlsx
+++ b/artfynd/A 59271-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136954257</v>
       </c>
       <c r="B3" t="n">
-        <v>108194</v>
+        <v>108195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59271-2025 artfynd.xlsx
+++ b/artfynd/A 59271-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136954257</v>
       </c>
       <c r="B3" t="n">
-        <v>108195</v>
+        <v>108207</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136954258</v>
       </c>
       <c r="B4" t="n">
-        <v>98347</v>
+        <v>98359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136954251</v>
       </c>
       <c r="B5" t="n">
-        <v>100083</v>
+        <v>100095</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136954253</v>
       </c>
       <c r="B6" t="n">
-        <v>100083</v>
+        <v>100095</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136954254</v>
       </c>
       <c r="B7" t="n">
-        <v>100083</v>
+        <v>100095</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136954255</v>
       </c>
       <c r="B8" t="n">
-        <v>100083</v>
+        <v>100095</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136954256</v>
       </c>
       <c r="B9" t="n">
-        <v>100083</v>
+        <v>100095</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>136954252</v>
       </c>
       <c r="B10" t="n">
-        <v>99455</v>
+        <v>99467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59271-2025 artfynd.xlsx
+++ b/artfynd/A 59271-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136954257</v>
       </c>
       <c r="B3" t="n">
-        <v>108207</v>
+        <v>108208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136954258</v>
       </c>
       <c r="B4" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136954251</v>
       </c>
       <c r="B5" t="n">
-        <v>100095</v>
+        <v>100096</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136954253</v>
       </c>
       <c r="B6" t="n">
-        <v>100095</v>
+        <v>100096</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136954254</v>
       </c>
       <c r="B7" t="n">
-        <v>100095</v>
+        <v>100096</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136954255</v>
       </c>
       <c r="B8" t="n">
-        <v>100095</v>
+        <v>100096</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136954256</v>
       </c>
       <c r="B9" t="n">
-        <v>100095</v>
+        <v>100096</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>136954252</v>
       </c>
       <c r="B10" t="n">
-        <v>99467</v>
+        <v>99468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59271-2025 artfynd.xlsx
+++ b/artfynd/A 59271-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136954257</v>
       </c>
       <c r="B3" t="n">
-        <v>108208</v>
+        <v>108211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136954258</v>
       </c>
       <c r="B4" t="n">
-        <v>98360</v>
+        <v>98363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136954251</v>
       </c>
       <c r="B5" t="n">
-        <v>100096</v>
+        <v>100099</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136954253</v>
       </c>
       <c r="B6" t="n">
-        <v>100096</v>
+        <v>100099</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136954254</v>
       </c>
       <c r="B7" t="n">
-        <v>100096</v>
+        <v>100099</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136954255</v>
       </c>
       <c r="B8" t="n">
-        <v>100096</v>
+        <v>100099</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136954256</v>
       </c>
       <c r="B9" t="n">
-        <v>100096</v>
+        <v>100099</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>136954252</v>
       </c>
       <c r="B10" t="n">
-        <v>99468</v>
+        <v>99471</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59271-2025 artfynd.xlsx
+++ b/artfynd/A 59271-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136954257</v>
       </c>
       <c r="B3" t="n">
-        <v>108211</v>
+        <v>108213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136954258</v>
       </c>
       <c r="B4" t="n">
-        <v>98363</v>
+        <v>98364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136954251</v>
       </c>
       <c r="B5" t="n">
-        <v>100099</v>
+        <v>100100</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136954253</v>
       </c>
       <c r="B6" t="n">
-        <v>100099</v>
+        <v>100100</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136954254</v>
       </c>
       <c r="B7" t="n">
-        <v>100099</v>
+        <v>100100</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136954255</v>
       </c>
       <c r="B8" t="n">
-        <v>100099</v>
+        <v>100100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136954256</v>
       </c>
       <c r="B9" t="n">
-        <v>100099</v>
+        <v>100100</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>136954252</v>
       </c>
       <c r="B10" t="n">
-        <v>99471</v>
+        <v>99472</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59271-2025 artfynd.xlsx
+++ b/artfynd/A 59271-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136954257</v>
       </c>
       <c r="B3" t="n">
-        <v>108213</v>
+        <v>108217</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136954258</v>
       </c>
       <c r="B4" t="n">
-        <v>98364</v>
+        <v>98367</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136954251</v>
       </c>
       <c r="B5" t="n">
-        <v>100100</v>
+        <v>100103</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136954253</v>
       </c>
       <c r="B6" t="n">
-        <v>100100</v>
+        <v>100103</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136954254</v>
       </c>
       <c r="B7" t="n">
-        <v>100100</v>
+        <v>100103</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136954255</v>
       </c>
       <c r="B8" t="n">
-        <v>100100</v>
+        <v>100103</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136954256</v>
       </c>
       <c r="B9" t="n">
-        <v>100100</v>
+        <v>100103</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>136954252</v>
       </c>
       <c r="B10" t="n">
-        <v>99472</v>
+        <v>99475</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
